--- a/freeCodeCamp/Vocabulario_Completo.xlsx
+++ b/freeCodeCamp/Vocabulario_Completo.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
@@ -42062,4 +42063,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/freeCodeCamp/Vocabulario_Completo.xlsx
+++ b/freeCodeCamp/Vocabulario_Completo.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uuario\Documents\workspace\EnglishDeveloper\freeCodeCamp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32289E94-E3CF-4DD3-AA37-245CB0FE0934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="3009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="3013">
   <si>
     <t>Ranking</t>
   </si>
@@ -9092,11 +9086,23 @@
   <si>
     <t>/'pro-vaids/</t>
   </si>
+  <si>
+    <t>/'pren-se-po_l/</t>
+  </si>
+  <si>
+    <t>/'kui-ri/</t>
+  </si>
+  <si>
+    <t>/'mein-nes/</t>
+  </si>
+  <si>
+    <t>mantenimiento</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -9202,9 +9208,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9242,7 +9248,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -9314,7 +9320,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9487,7 +9493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I2947"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10420,11 +10426,14 @@
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C77">
         <v>112</v>
+      </c>
+      <c r="D77" t="s">
+        <v>3009</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -21190,11 +21199,14 @@
       <c r="A1050">
         <v>1049</v>
       </c>
-      <c r="B1050" t="s">
+      <c r="B1050" s="2" t="s">
         <v>1057</v>
       </c>
       <c r="C1050">
         <v>6</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>3010</v>
       </c>
     </row>
     <row r="1051" spans="1:6" x14ac:dyDescent="0.25">
@@ -24975,7 +24987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1393">
         <v>1392</v>
       </c>
@@ -24986,7 +24998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1394">
         <v>1393</v>
       </c>
@@ -24997,7 +25009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1395">
         <v>1394</v>
       </c>
@@ -25008,7 +25020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1396">
         <v>1395</v>
       </c>
@@ -25019,7 +25031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1397">
         <v>1396</v>
       </c>
@@ -25030,7 +25042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1398">
         <v>1397</v>
       </c>
@@ -25041,18 +25053,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1399">
         <v>1398</v>
       </c>
-      <c r="B1399" t="s">
+      <c r="B1399" s="2" t="s">
         <v>1406</v>
       </c>
       <c r="C1399">
         <v>3</v>
       </c>
-    </row>
-    <row r="1400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1399" t="s">
+        <v>3011</v>
+      </c>
+      <c r="E1399" t="s">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1400">
         <v>1399</v>
       </c>
@@ -25063,7 +25081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1401">
         <v>1400</v>
       </c>
@@ -25074,7 +25092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1402">
         <v>1401</v>
       </c>
@@ -25085,7 +25103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1403">
         <v>1402</v>
       </c>
@@ -25096,7 +25114,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1404">
         <v>1403</v>
       </c>
@@ -25107,7 +25125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1405">
         <v>1404</v>
       </c>
@@ -25118,7 +25136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1406">
         <v>1405</v>
       </c>
@@ -25129,7 +25147,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1407">
         <v>1406</v>
       </c>
@@ -25140,7 +25158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1408">
         <v>1407</v>
       </c>
@@ -42102,14 +42120,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I2947" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I2947"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/freeCodeCamp/Vocabulario_Completo.xlsx
+++ b/freeCodeCamp/Vocabulario_Completo.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="3013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="3014">
   <si>
     <t>Ranking</t>
   </si>
@@ -9097,6 +9097,9 @@
   </si>
   <si>
     <t>mantenimiento</t>
+  </si>
+  <si>
+    <t>/'vi-e-c_ol/</t>
   </si>
 </sst>
 </file>
@@ -11311,11 +11314,14 @@
       <c r="A155">
         <v>154</v>
       </c>
-      <c r="B155" t="s">
+      <c r="B155" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C155">
         <v>61</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>3013</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">

--- a/freeCodeCamp/Vocabulario_Completo.xlsx
+++ b/freeCodeCamp/Vocabulario_Completo.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="3119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="3121">
   <si>
     <t>Ranking</t>
   </si>
@@ -9415,6 +9415,12 @@
   </si>
   <si>
     <t>/en-'chur/</t>
+  </si>
+  <si>
+    <t>borrador</t>
+  </si>
+  <si>
+    <t>/draft/</t>
   </si>
 </sst>
 </file>
@@ -15001,7 +15007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>448</v>
       </c>
@@ -15012,7 +15018,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>449</v>
       </c>
@@ -15023,7 +15029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>450</v>
       </c>
@@ -15034,7 +15040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>451</v>
       </c>
@@ -15045,7 +15051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>452</v>
       </c>
@@ -15056,7 +15062,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>453</v>
       </c>
@@ -15067,7 +15073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>454</v>
       </c>
@@ -15078,7 +15084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>455</v>
       </c>
@@ -15089,7 +15095,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>456</v>
       </c>
@@ -15100,7 +15106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>457</v>
       </c>
@@ -15111,7 +15117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>458</v>
       </c>
@@ -15122,7 +15128,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>459</v>
       </c>
@@ -15133,7 +15139,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>460</v>
       </c>
@@ -15144,18 +15150,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>461</v>
       </c>
-      <c r="B462" t="s">
+      <c r="B462" s="2" t="s">
         <v>469</v>
       </c>
       <c r="C462">
         <v>20</v>
       </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D462" t="s">
+        <v>3119</v>
+      </c>
+      <c r="E462" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>462</v>
       </c>
@@ -15166,7 +15178,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>463</v>
       </c>
